--- a/outputs/penalizaciones-financiacion-plantilla/Plantilla_penalizaciones_financiacion.xlsx
+++ b/outputs/penalizaciones-financiacion-plantilla/Plantilla_penalizaciones_financiacion.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penalizaciones" sheetId="1" r:id="R18bd30057a5d4f4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penalizaciones" sheetId="1" r:id="Rd9fccbbf1d9443df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -285,10 +285,10 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -519,10 +519,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -533,242 +534,275 @@
       <x:c r="C1" s="4"/>
       <x:c r="D1" s="4"/>
       <x:c r="E1" s="4"/>
+      <x:c r="F1" s="4"/>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Completa una fila por penalizacion. Las columnas A, B, C y D son obligatorias.</x:v>
+        <x:v>Completa una fila por penalizacion. Mes, Email comercial e importe son obligatorios.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
       <x:c r="D2" s="8"/>
       <x:c r="E2" s="8"/>
+      <x:c r="F2" s="8"/>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
       <x:c r="A3" s="12" t="str">
-        <x:v>Mes comision: usa YYYY-MM (ejemplo: 2026-06). ID comercial: usa el ID de Salesforce del propietario de las oportunidades.</x:v>
+        <x:v>Mes comision: usa YYYY-MM (ejemplo: 2026-06). Email comercial: debe coincidir con User.Email en Salesforce.</x:v>
       </x:c>
       <x:c r="B3" s="12"/>
       <x:c r="C3" s="12"/>
       <x:c r="D3" s="12"/>
       <x:c r="E3" s="12"/>
+      <x:c r="F3" s="12"/>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>descontar comercial 4%: introduce el importe a descontar. Puede ser positivo o negativo; el sistema siempre lo aplicara como penalizacion negativa. Varias filas del mismo ID y mes se suman.</x:v>
+        <x:v>descontar comercial 4%: introduce el importe a descontar. Puede ser positivo o negativo; el sistema siempre lo aplicara como penalizacion negativa. Nombre e ID Salesforce son opcionales y solo sirven para auditoria.</x:v>
       </x:c>
       <x:c r="B4" s="12"/>
       <x:c r="C4" s="12"/>
       <x:c r="D4" s="12"/>
       <x:c r="E4" s="12"/>
+      <x:c r="F4" s="12"/>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Mes comision</x:v>
       </x:c>
       <x:c r="B6" s="25" t="str">
-        <x:v>Nombre comercial</x:v>
+        <x:v>Email comercial</x:v>
       </x:c>
       <x:c r="C6" s="25" t="str">
-        <x:v>ID comercial</x:v>
+        <x:v>Nombre comercial (opcional)</x:v>
       </x:c>
       <x:c r="D6" s="25" t="str">
+        <x:v>ID Salesforce (opcional)</x:v>
+      </x:c>
+      <x:c r="E6" s="25" t="str">
         <x:v>descontar comercial 4%</x:v>
       </x:c>
-      <x:c r="E6" s="26" t="str">
+      <x:c r="F6" s="26" t="str">
         <x:v>Observacion (opcional)</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="37"/>
-      <x:c r="B7" s="40"/>
-      <x:c r="C7" s="40"/>
-      <x:c r="D7" s="46"/>
-      <x:c r="E7" s="49"/>
+      <x:c r="B7" s="38"/>
+      <x:c r="C7" s="38"/>
+      <x:c r="D7" s="38"/>
+      <x:c r="E7" s="46"/>
+      <x:c r="F7" s="49"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="38"/>
-      <x:c r="B8" s="41"/>
-      <x:c r="C8" s="41"/>
-      <x:c r="D8" s="47"/>
-      <x:c r="E8" s="50"/>
+      <x:c r="A8" s="39"/>
+      <x:c r="B8" s="40"/>
+      <x:c r="C8" s="40"/>
+      <x:c r="D8" s="40"/>
+      <x:c r="E8" s="47"/>
+      <x:c r="F8" s="50"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="38"/>
-      <x:c r="B9" s="41"/>
-      <x:c r="C9" s="41"/>
-      <x:c r="D9" s="47"/>
-      <x:c r="E9" s="50"/>
+      <x:c r="A9" s="39"/>
+      <x:c r="B9" s="40"/>
+      <x:c r="C9" s="40"/>
+      <x:c r="D9" s="40"/>
+      <x:c r="E9" s="47"/>
+      <x:c r="F9" s="50"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="38"/>
-      <x:c r="B10" s="41"/>
-      <x:c r="C10" s="41"/>
-      <x:c r="D10" s="47"/>
-      <x:c r="E10" s="50"/>
+      <x:c r="A10" s="39"/>
+      <x:c r="B10" s="40"/>
+      <x:c r="C10" s="40"/>
+      <x:c r="D10" s="40"/>
+      <x:c r="E10" s="47"/>
+      <x:c r="F10" s="50"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="38"/>
-      <x:c r="B11" s="41"/>
-      <x:c r="C11" s="41"/>
-      <x:c r="D11" s="47"/>
-      <x:c r="E11" s="50"/>
+      <x:c r="A11" s="39"/>
+      <x:c r="B11" s="40"/>
+      <x:c r="C11" s="40"/>
+      <x:c r="D11" s="40"/>
+      <x:c r="E11" s="47"/>
+      <x:c r="F11" s="50"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="38"/>
-      <x:c r="B12" s="41"/>
-      <x:c r="C12" s="41"/>
-      <x:c r="D12" s="47"/>
-      <x:c r="E12" s="50"/>
+      <x:c r="A12" s="39"/>
+      <x:c r="B12" s="40"/>
+      <x:c r="C12" s="40"/>
+      <x:c r="D12" s="40"/>
+      <x:c r="E12" s="47"/>
+      <x:c r="F12" s="50"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="38"/>
-      <x:c r="B13" s="41"/>
-      <x:c r="C13" s="41"/>
-      <x:c r="D13" s="47"/>
-      <x:c r="E13" s="50"/>
+      <x:c r="A13" s="39"/>
+      <x:c r="B13" s="40"/>
+      <x:c r="C13" s="40"/>
+      <x:c r="D13" s="40"/>
+      <x:c r="E13" s="47"/>
+      <x:c r="F13" s="50"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="38"/>
-      <x:c r="B14" s="41"/>
-      <x:c r="C14" s="41"/>
-      <x:c r="D14" s="47"/>
-      <x:c r="E14" s="50"/>
+      <x:c r="A14" s="39"/>
+      <x:c r="B14" s="40"/>
+      <x:c r="C14" s="40"/>
+      <x:c r="D14" s="40"/>
+      <x:c r="E14" s="47"/>
+      <x:c r="F14" s="50"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="38"/>
-      <x:c r="B15" s="41"/>
-      <x:c r="C15" s="41"/>
-      <x:c r="D15" s="47"/>
-      <x:c r="E15" s="50"/>
+      <x:c r="A15" s="39"/>
+      <x:c r="B15" s="40"/>
+      <x:c r="C15" s="40"/>
+      <x:c r="D15" s="40"/>
+      <x:c r="E15" s="47"/>
+      <x:c r="F15" s="50"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="38"/>
-      <x:c r="B16" s="41"/>
-      <x:c r="C16" s="41"/>
-      <x:c r="D16" s="47"/>
-      <x:c r="E16" s="50"/>
+      <x:c r="A16" s="39"/>
+      <x:c r="B16" s="40"/>
+      <x:c r="C16" s="40"/>
+      <x:c r="D16" s="40"/>
+      <x:c r="E16" s="47"/>
+      <x:c r="F16" s="50"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="38"/>
-      <x:c r="B17" s="41"/>
-      <x:c r="C17" s="41"/>
-      <x:c r="D17" s="47"/>
-      <x:c r="E17" s="50"/>
+      <x:c r="A17" s="39"/>
+      <x:c r="B17" s="40"/>
+      <x:c r="C17" s="40"/>
+      <x:c r="D17" s="40"/>
+      <x:c r="E17" s="47"/>
+      <x:c r="F17" s="50"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="38"/>
-      <x:c r="B18" s="41"/>
-      <x:c r="C18" s="41"/>
-      <x:c r="D18" s="47"/>
-      <x:c r="E18" s="50"/>
+      <x:c r="A18" s="39"/>
+      <x:c r="B18" s="40"/>
+      <x:c r="C18" s="40"/>
+      <x:c r="D18" s="40"/>
+      <x:c r="E18" s="47"/>
+      <x:c r="F18" s="50"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="38"/>
-      <x:c r="B19" s="41"/>
-      <x:c r="C19" s="41"/>
-      <x:c r="D19" s="47"/>
-      <x:c r="E19" s="50"/>
+      <x:c r="A19" s="39"/>
+      <x:c r="B19" s="40"/>
+      <x:c r="C19" s="40"/>
+      <x:c r="D19" s="40"/>
+      <x:c r="E19" s="47"/>
+      <x:c r="F19" s="50"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="38"/>
-      <x:c r="B20" s="41"/>
-      <x:c r="C20" s="41"/>
-      <x:c r="D20" s="47"/>
-      <x:c r="E20" s="50"/>
+      <x:c r="A20" s="39"/>
+      <x:c r="B20" s="40"/>
+      <x:c r="C20" s="40"/>
+      <x:c r="D20" s="40"/>
+      <x:c r="E20" s="47"/>
+      <x:c r="F20" s="50"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="38"/>
-      <x:c r="B21" s="41"/>
-      <x:c r="C21" s="41"/>
-      <x:c r="D21" s="47"/>
-      <x:c r="E21" s="50"/>
+      <x:c r="A21" s="39"/>
+      <x:c r="B21" s="40"/>
+      <x:c r="C21" s="40"/>
+      <x:c r="D21" s="40"/>
+      <x:c r="E21" s="47"/>
+      <x:c r="F21" s="50"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="38"/>
-      <x:c r="B22" s="41"/>
-      <x:c r="C22" s="41"/>
-      <x:c r="D22" s="47"/>
-      <x:c r="E22" s="50"/>
+      <x:c r="A22" s="39"/>
+      <x:c r="B22" s="40"/>
+      <x:c r="C22" s="40"/>
+      <x:c r="D22" s="40"/>
+      <x:c r="E22" s="47"/>
+      <x:c r="F22" s="50"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="38"/>
-      <x:c r="B23" s="41"/>
-      <x:c r="C23" s="41"/>
-      <x:c r="D23" s="47"/>
-      <x:c r="E23" s="50"/>
+      <x:c r="A23" s="39"/>
+      <x:c r="B23" s="40"/>
+      <x:c r="C23" s="40"/>
+      <x:c r="D23" s="40"/>
+      <x:c r="E23" s="47"/>
+      <x:c r="F23" s="50"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="38"/>
-      <x:c r="B24" s="41"/>
-      <x:c r="C24" s="41"/>
-      <x:c r="D24" s="47"/>
-      <x:c r="E24" s="50"/>
+      <x:c r="A24" s="39"/>
+      <x:c r="B24" s="40"/>
+      <x:c r="C24" s="40"/>
+      <x:c r="D24" s="40"/>
+      <x:c r="E24" s="47"/>
+      <x:c r="F24" s="50"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="38"/>
-      <x:c r="B25" s="41"/>
-      <x:c r="C25" s="41"/>
-      <x:c r="D25" s="47"/>
-      <x:c r="E25" s="50"/>
+      <x:c r="A25" s="39"/>
+      <x:c r="B25" s="40"/>
+      <x:c r="C25" s="40"/>
+      <x:c r="D25" s="40"/>
+      <x:c r="E25" s="47"/>
+      <x:c r="F25" s="50"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="38"/>
-      <x:c r="B26" s="41"/>
-      <x:c r="C26" s="41"/>
-      <x:c r="D26" s="47"/>
-      <x:c r="E26" s="50"/>
+      <x:c r="A26" s="39"/>
+      <x:c r="B26" s="40"/>
+      <x:c r="C26" s="40"/>
+      <x:c r="D26" s="40"/>
+      <x:c r="E26" s="47"/>
+      <x:c r="F26" s="50"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="38"/>
-      <x:c r="B27" s="41"/>
-      <x:c r="C27" s="41"/>
-      <x:c r="D27" s="47"/>
-      <x:c r="E27" s="50"/>
+      <x:c r="A27" s="39"/>
+      <x:c r="B27" s="40"/>
+      <x:c r="C27" s="40"/>
+      <x:c r="D27" s="40"/>
+      <x:c r="E27" s="47"/>
+      <x:c r="F27" s="50"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="38"/>
-      <x:c r="B28" s="41"/>
-      <x:c r="C28" s="41"/>
-      <x:c r="D28" s="47"/>
-      <x:c r="E28" s="50"/>
+      <x:c r="A28" s="39"/>
+      <x:c r="B28" s="40"/>
+      <x:c r="C28" s="40"/>
+      <x:c r="D28" s="40"/>
+      <x:c r="E28" s="47"/>
+      <x:c r="F28" s="50"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="38"/>
-      <x:c r="B29" s="41"/>
-      <x:c r="C29" s="41"/>
-      <x:c r="D29" s="47"/>
-      <x:c r="E29" s="50"/>
+      <x:c r="A29" s="39"/>
+      <x:c r="B29" s="40"/>
+      <x:c r="C29" s="40"/>
+      <x:c r="D29" s="40"/>
+      <x:c r="E29" s="47"/>
+      <x:c r="F29" s="50"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="38"/>
-      <x:c r="B30" s="41"/>
-      <x:c r="C30" s="41"/>
-      <x:c r="D30" s="47"/>
-      <x:c r="E30" s="50"/>
+      <x:c r="A30" s="39"/>
+      <x:c r="B30" s="40"/>
+      <x:c r="C30" s="40"/>
+      <x:c r="D30" s="40"/>
+      <x:c r="E30" s="47"/>
+      <x:c r="F30" s="50"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="39"/>
+      <x:c r="A31" s="41"/>
       <x:c r="B31" s="42"/>
       <x:c r="C31" s="42"/>
-      <x:c r="D31" s="48"/>
-      <x:c r="E31" s="51"/>
+      <x:c r="D31" s="42"/>
+      <x:c r="E31" s="48"/>
+      <x:c r="F31" s="51"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="54" t="str">
-        <x:v>Ejemplo de una fila valida: 2026-06 | Comercial Uno | 005XXXXXXXXXXXX | 125,50 | Cancelacion anticipada</x:v>
+        <x:v>Ejemplo de una fila valida: 2026-06 | comercial@hrmotor.com | Comercial Uno | 005XXXXXXXXXXXX | 125,50 | Cancelacion anticipada</x:v>
       </x:c>
       <x:c r="B33" s="54"/>
       <x:c r="C33" s="54"/>
       <x:c r="D33" s="54"/>
       <x:c r="E33" s="54"/>
+      <x:c r="F33" s="54"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-    <x:mergeCell ref="A2:E2"/>
-    <x:mergeCell ref="A3:E3"/>
-    <x:mergeCell ref="A4:E4"/>
-    <x:mergeCell ref="A33:E33"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A3:F3"/>
+    <x:mergeCell ref="A4:F4"/>
+    <x:mergeCell ref="A33:F33"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
